--- a/training_survey_templates/040_fitness_performance_training_evaluation_form--training_survey_templates.xlsx
+++ b/training_survey_templates/040_fitness_performance_training_evaluation_form--training_survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -629,12 +629,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'questions_1',_'label':_'what_was_your_motivation_for_starting_your_fitness_journey?',_'type':_'select_one',_'options':_[{'id':_211,_'label':_'to_improve_overall_health'},_{'id':_212,_'label':_'to_enhance_athletic_performance'}]}</t>
+          <t>what_was_your_motivation_for_starting_your_fitness_journey?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'questions_1', 'label': 'What was your motivation for starting your fitness journey?', 'type': 'select_one', 'options': [{'id': 211, 'label': 'To improve overall health'}, {'id': 212, 'label': 'To enhance athletic performance'}]}</t>
+          <t>What was your motivation for starting your fitness journey?</t>
         </is>
       </c>
     </row>
@@ -646,12 +646,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'question_2',_'label':_'how_many_times_do_you_work_out_per_week?',_'type':_'integer',_'options':_[]}</t>
+          <t>how_many_times_do_you_work_out_per_week?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'question_2', 'label': 'How many times do you work out per week?', 'type': 'integer', 'options': []}</t>
+          <t>How many times do you work out per week?</t>
         </is>
       </c>
     </row>
@@ -663,12 +663,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'question_3',_'label':_'how_many_days_do_you_work_out_per_week?',_'type':_'integer',_'options':_[]}</t>
+          <t>how_many_days_do_you_work_out_per_week?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'question_3', 'label': 'How many days do you work out per week?', 'type': 'integer', 'options': []}</t>
+          <t>How many days do you work out per week?</t>
         </is>
       </c>
     </row>
@@ -680,12 +680,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'question_4',_'label':_'do_you_do_strength_training_exercises?',_'type':_'select_multiple',_'options':_[{'id':_241,_'label':_true},_{'id':_242,_'label':_false}]}</t>
+          <t>do_you_do_strength_training_exercises?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'question_4', 'label': 'Do you do strength training exercises?', 'type': 'select_multiple', 'options': [{'id': 241, 'label': True}, {'id': 242, 'label': False}]}</t>
+          <t>Do you do strength training exercises?</t>
         </is>
       </c>
     </row>
@@ -697,12 +697,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'note',_'label':_'additional_information',_'type':_'note',_'options':_[]}</t>
+          <t>additional_information</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': 'note', 'label': 'Additional Information', 'type': 'note', 'options': []}</t>
+          <t>Additional Information</t>
         </is>
       </c>
     </row>
